--- a/nba_data_raw.xlsx
+++ b/nba_data_raw.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3C95A45-8E34-4C90-9FAF-B49748ECE4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/preetishrath/Desktop/aberdeen/nba-analytics-assignment/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AED70E5-DB62-254B-A15C-D4CA110FA1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2580" yWindow="2580" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Start Here" sheetId="1" r:id="rId1"/>
@@ -1649,9 +1654,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Issue 4 — duplicate records</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -1771,13 +1773,16 @@
   </si>
   <si>
     <t>💡 TIP: Enter stats for 2-3 players to compare them. The player with the highest "Bang for Buck" is usually your best recommendation.</t>
+  </si>
+  <si>
+    <t>Issue 4 — games started &gt; games played</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1790,153 +1795,180 @@
       <sz val="16"/>
       <color rgb="FFFFC72C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9CB3D4"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1D428A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1D428A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1A1F2E"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFC72C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC8102E"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF00600D"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF8B6000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFC72C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFC72C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1A1F2E"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FFAAAAAA"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1A7A3F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1D428A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1A7A3F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFC72C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1D428A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF8A96A8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1A7A3F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1A7A3F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF8B6000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2172,15 +2204,14 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2194,6 +2225,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2229,9 +2264,6 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2535,7 +2567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -2544,92 +2576,92 @@
     <col min="5" max="5" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="8.1" customHeight="1"/>
-    <row r="2" spans="2:4" ht="38.1" customHeight="1">
-      <c r="B2" s="42" t="s">
+    <row r="1" spans="2:4" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-    </row>
-    <row r="3" spans="2:4" ht="21.95" customHeight="1">
-      <c r="B3" s="45" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+    </row>
+    <row r="3" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-    </row>
-    <row r="4" spans="2:4" ht="12" customHeight="1"/>
-    <row r="5" spans="2:4" ht="26.1" customHeight="1">
-      <c r="B5" s="46" t="s">
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+    </row>
+    <row r="4" spans="2:4" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-    </row>
-    <row r="6" spans="2:4" ht="21.95" customHeight="1">
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="60"/>
-    </row>
-    <row r="7" spans="2:4" ht="21.95" customHeight="1">
+      <c r="D6" s="42"/>
+    </row>
+    <row r="7" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="60"/>
-    </row>
-    <row r="8" spans="2:4" ht="21.95" customHeight="1">
+      <c r="D7" s="42"/>
+    </row>
+    <row r="8" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="60"/>
-    </row>
-    <row r="9" spans="2:4" ht="21.95" customHeight="1">
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="60"/>
-    </row>
-    <row r="10" spans="2:4" ht="21.95" customHeight="1">
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="60"/>
-    </row>
-    <row r="11" spans="2:4" ht="21.95" customHeight="1">
+      <c r="D10" s="42"/>
+    </row>
+    <row r="11" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="60"/>
-    </row>
-    <row r="12" spans="2:4" ht="14.1" customHeight="1"/>
-    <row r="13" spans="2:4" ht="26.1" customHeight="1">
-      <c r="B13" s="43" t="s">
+      <c r="D11" s="42"/>
+    </row>
+    <row r="12" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-    </row>
-    <row r="14" spans="2:4" ht="21.95" customHeight="1">
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+    </row>
+    <row r="14" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>16</v>
       </c>
@@ -2640,7 +2672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="72" customHeight="1">
+    <row r="15" spans="2:4" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
         <v>19</v>
       </c>
@@ -2651,7 +2683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="72" customHeight="1">
+    <row r="16" spans="2:4" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
         <v>22</v>
       </c>
@@ -2662,7 +2694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="72" customHeight="1">
+    <row r="17" spans="2:4" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
@@ -2673,7 +2705,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="72" customHeight="1">
+    <row r="18" spans="2:4" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2684,13 +2716,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="14.1" customHeight="1"/>
-    <row r="20" spans="2:4" ht="36" customHeight="1">
-      <c r="B20" s="40" t="s">
+    <row r="19" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2713,7 +2745,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T434"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2735,32 +2767,32 @@
     <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="32.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-    </row>
-    <row r="2" spans="1:20" ht="14.1" customHeight="1"/>
-    <row r="3" spans="1:20">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+    </row>
+    <row r="2" spans="1:20" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>33</v>
       </c>
@@ -2822,7 +2854,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>1345</v>
       </c>
@@ -2884,7 +2916,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>1230</v>
       </c>
@@ -2946,7 +2978,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>1058</v>
       </c>
@@ -3008,7 +3040,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>1068</v>
       </c>
@@ -3070,7 +3102,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>1016</v>
       </c>
@@ -3132,7 +3164,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>1263</v>
       </c>
@@ -3194,7 +3226,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>1425</v>
       </c>
@@ -3252,7 +3284,7 @@
       </c>
       <c r="T10" s="11"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>1112</v>
       </c>
@@ -3314,7 +3346,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>1348</v>
       </c>
@@ -3376,7 +3408,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>1164</v>
       </c>
@@ -3438,7 +3470,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>1196</v>
       </c>
@@ -3500,7 +3532,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>1035</v>
       </c>
@@ -3562,7 +3594,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
         <v>1052</v>
       </c>
@@ -3624,7 +3656,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>1320</v>
       </c>
@@ -3686,7 +3718,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>1331</v>
       </c>
@@ -3748,7 +3780,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>1069</v>
       </c>
@@ -3810,7 +3842,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
         <v>1368</v>
       </c>
@@ -3872,7 +3904,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>1273</v>
       </c>
@@ -3934,7 +3966,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>1033</v>
       </c>
@@ -3996,7 +4028,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>1000</v>
       </c>
@@ -4058,7 +4090,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>1153</v>
       </c>
@@ -4120,7 +4152,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>1017</v>
       </c>
@@ -4182,7 +4214,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>1405</v>
       </c>
@@ -4244,7 +4276,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>1081</v>
       </c>
@@ -4306,7 +4338,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
         <v>1009</v>
       </c>
@@ -4368,7 +4400,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>1214</v>
       </c>
@@ -4430,7 +4462,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>1088</v>
       </c>
@@ -4492,7 +4524,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>1229</v>
       </c>
@@ -4554,7 +4586,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>1290</v>
       </c>
@@ -4616,7 +4648,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>1015</v>
       </c>
@@ -4678,7 +4710,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>1155</v>
       </c>
@@ -4740,7 +4772,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>1341</v>
       </c>
@@ -4802,7 +4834,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>1372</v>
       </c>
@@ -4864,7 +4896,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>1371</v>
       </c>
@@ -4926,7 +4958,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>1362</v>
       </c>
@@ -4988,7 +5020,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>1359</v>
       </c>
@@ -5050,7 +5082,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>1005</v>
       </c>
@@ -5112,7 +5144,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>1275</v>
       </c>
@@ -5174,7 +5206,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>1261</v>
       </c>
@@ -5236,7 +5268,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>1395</v>
       </c>
@@ -5298,7 +5330,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>1071</v>
       </c>
@@ -5360,7 +5392,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>1244</v>
       </c>
@@ -5422,7 +5454,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>1304</v>
       </c>
@@ -5484,7 +5516,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>1423</v>
       </c>
@@ -5546,7 +5578,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>1311</v>
       </c>
@@ -5608,7 +5640,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>1107</v>
       </c>
@@ -5670,7 +5702,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>1354</v>
       </c>
@@ -5732,7 +5764,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>1095</v>
       </c>
@@ -5794,7 +5826,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>1082</v>
       </c>
@@ -5856,7 +5888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>1334</v>
       </c>
@@ -5918,7 +5950,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="11">
         <v>1186</v>
       </c>
@@ -5980,7 +6012,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>1430</v>
       </c>
@@ -6042,7 +6074,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" s="11">
         <v>1323</v>
       </c>
@@ -6104,7 +6136,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>1156</v>
       </c>
@@ -6166,7 +6198,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" s="11">
         <v>1409</v>
       </c>
@@ -6228,7 +6260,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>1347</v>
       </c>
@@ -6290,7 +6322,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" s="11">
         <v>1146</v>
       </c>
@@ -6352,7 +6384,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>1085</v>
       </c>
@@ -6414,7 +6446,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" s="11">
         <v>1142</v>
       </c>
@@ -6476,7 +6508,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>1132</v>
       </c>
@@ -6538,7 +6570,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" s="11">
         <v>1424</v>
       </c>
@@ -6600,7 +6632,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>1210</v>
       </c>
@@ -6662,7 +6694,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" s="11">
         <v>1185</v>
       </c>
@@ -6724,7 +6756,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>1404</v>
       </c>
@@ -6786,7 +6818,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" s="11">
         <v>1167</v>
       </c>
@@ -6848,7 +6880,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>1079</v>
       </c>
@@ -6910,7 +6942,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" s="11">
         <v>1099</v>
       </c>
@@ -6972,7 +7004,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>1114</v>
       </c>
@@ -7034,7 +7066,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="72" spans="1:20">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <v>1044</v>
       </c>
@@ -7096,7 +7128,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>1097</v>
       </c>
@@ -7158,7 +7190,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" s="11">
         <v>1125</v>
       </c>
@@ -7220,7 +7252,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>1295</v>
       </c>
@@ -7282,7 +7314,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="11">
         <v>1098</v>
       </c>
@@ -7344,7 +7376,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>1197</v>
       </c>
@@ -7406,7 +7438,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" s="11">
         <v>1008</v>
       </c>
@@ -7468,7 +7500,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>1177</v>
       </c>
@@ -7530,7 +7562,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" s="11">
         <v>1040</v>
       </c>
@@ -7592,7 +7624,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>1073</v>
       </c>
@@ -7654,7 +7686,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" s="11">
         <v>1262</v>
       </c>
@@ -7716,7 +7748,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>1176</v>
       </c>
@@ -7778,7 +7810,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" s="11">
         <v>1172</v>
       </c>
@@ -7840,7 +7872,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>1007</v>
       </c>
@@ -7902,7 +7934,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="86" spans="1:20">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86" s="11">
         <v>1266</v>
       </c>
@@ -7964,7 +7996,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="87" spans="1:20">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>1218</v>
       </c>
@@ -8026,7 +8058,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" s="11">
         <v>1387</v>
       </c>
@@ -8088,7 +8120,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="89" spans="1:20">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>1212</v>
       </c>
@@ -8150,7 +8182,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:20">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" s="11">
         <v>1194</v>
       </c>
@@ -8212,7 +8244,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="91" spans="1:20">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>1421</v>
       </c>
@@ -8274,7 +8306,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92" s="11">
         <v>1051</v>
       </c>
@@ -8336,7 +8368,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>1279</v>
       </c>
@@ -8398,7 +8430,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:20">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94" s="11">
         <v>1209</v>
       </c>
@@ -8460,7 +8492,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="95" spans="1:20">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>1256</v>
       </c>
@@ -8522,7 +8554,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:20">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A96" s="11">
         <v>1070</v>
       </c>
@@ -8584,7 +8616,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>1355</v>
       </c>
@@ -8646,7 +8678,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="98" spans="1:20">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98" s="11">
         <v>1179</v>
       </c>
@@ -8708,7 +8740,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>1113</v>
       </c>
@@ -8770,7 +8802,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" s="11">
         <v>1418</v>
       </c>
@@ -8832,7 +8864,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>1408</v>
       </c>
@@ -8894,7 +8926,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:20">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" s="11">
         <v>1138</v>
       </c>
@@ -8956,7 +8988,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>1055</v>
       </c>
@@ -9018,7 +9050,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A104" s="11">
         <v>1281</v>
       </c>
@@ -9080,7 +9112,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>1388</v>
       </c>
@@ -9142,7 +9174,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="11">
         <v>1314</v>
       </c>
@@ -9204,7 +9236,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>1370</v>
       </c>
@@ -9266,7 +9298,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="108" spans="1:20">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="11">
         <v>1042</v>
       </c>
@@ -9328,7 +9360,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>1329</v>
       </c>
@@ -9390,7 +9422,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="11">
         <v>1050</v>
       </c>
@@ -9452,7 +9484,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="111" spans="1:20">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>1127</v>
       </c>
@@ -9514,7 +9546,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A112" s="11">
         <v>1419</v>
       </c>
@@ -9576,7 +9608,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="113" spans="1:20">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>1385</v>
       </c>
@@ -9638,7 +9670,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="114" spans="1:20">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" s="11">
         <v>1416</v>
       </c>
@@ -9700,7 +9732,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="115" spans="1:20">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>1025</v>
       </c>
@@ -9762,7 +9794,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:20">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" s="11">
         <v>1031</v>
       </c>
@@ -9824,7 +9856,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:20">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>1227</v>
       </c>
@@ -9886,7 +9918,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A118" s="11">
         <v>1238</v>
       </c>
@@ -9948,7 +9980,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>1110</v>
       </c>
@@ -10010,7 +10042,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="120" spans="1:20">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" s="11">
         <v>1233</v>
       </c>
@@ -10072,7 +10104,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="121" spans="1:20">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>1060</v>
       </c>
@@ -10134,7 +10166,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="122" spans="1:20">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A122" s="11">
         <v>1312</v>
       </c>
@@ -10196,7 +10228,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="123" spans="1:20">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>1056</v>
       </c>
@@ -10258,7 +10290,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A124" s="11">
         <v>1089</v>
       </c>
@@ -10320,7 +10352,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="125" spans="1:20">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>1330</v>
       </c>
@@ -10378,7 +10410,7 @@
       </c>
       <c r="T125" s="12"/>
     </row>
-    <row r="126" spans="1:20">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A126" s="11">
         <v>1208</v>
       </c>
@@ -10440,7 +10472,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:20">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>1174</v>
       </c>
@@ -10502,7 +10534,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="128" spans="1:20">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A128" s="11">
         <v>1303</v>
       </c>
@@ -10564,7 +10596,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="129" spans="1:20">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>1429</v>
       </c>
@@ -10626,7 +10658,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="130" spans="1:20">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A130" s="11">
         <v>1327</v>
       </c>
@@ -10688,7 +10720,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="131" spans="1:20">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>1203</v>
       </c>
@@ -10750,7 +10782,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="132" spans="1:20">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A132" s="11">
         <v>1121</v>
       </c>
@@ -10812,7 +10844,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="133" spans="1:20">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>1389</v>
       </c>
@@ -10874,7 +10906,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="134" spans="1:20">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A134" s="11">
         <v>1187</v>
       </c>
@@ -10936,7 +10968,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="135" spans="1:20">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>1148</v>
       </c>
@@ -10998,7 +11030,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="136" spans="1:20">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A136" s="11">
         <v>1147</v>
       </c>
@@ -11060,7 +11092,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="137" spans="1:20">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>1140</v>
       </c>
@@ -11122,7 +11154,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="138" spans="1:20">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" s="11">
         <v>1163</v>
       </c>
@@ -11184,7 +11216,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:20">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>1270</v>
       </c>
@@ -11246,7 +11278,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="140" spans="1:20">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" s="11">
         <v>1427</v>
       </c>
@@ -11308,7 +11340,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="141" spans="1:20">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>1123</v>
       </c>
@@ -11370,7 +11402,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="142" spans="1:20">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A142" s="11">
         <v>1053</v>
       </c>
@@ -11432,7 +11464,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="143" spans="1:20">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>1006</v>
       </c>
@@ -11494,7 +11526,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="144" spans="1:20">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A144" s="11">
         <v>1378</v>
       </c>
@@ -11556,7 +11588,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="145" spans="1:20">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>1296</v>
       </c>
@@ -11618,7 +11650,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:20">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A146" s="11">
         <v>1328</v>
       </c>
@@ -11680,7 +11712,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="147" spans="1:20">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>1316</v>
       </c>
@@ -11742,7 +11774,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="148" spans="1:20">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A148" s="11">
         <v>1249</v>
       </c>
@@ -11804,7 +11836,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="149" spans="1:20">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>1034</v>
       </c>
@@ -11866,7 +11898,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="150" spans="1:20">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A150" s="11">
         <v>1219</v>
       </c>
@@ -11928,7 +11960,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="151" spans="1:20">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>1399</v>
       </c>
@@ -11990,7 +12022,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="152" spans="1:20">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A152" s="11">
         <v>1151</v>
       </c>
@@ -12052,7 +12084,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="153" spans="1:20">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>1350</v>
       </c>
@@ -12114,7 +12146,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="154" spans="1:20">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A154" s="11">
         <v>1321</v>
       </c>
@@ -12176,7 +12208,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="155" spans="1:20">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>1365</v>
       </c>
@@ -12238,7 +12270,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="156" spans="1:20">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A156" s="11">
         <v>1124</v>
       </c>
@@ -12300,7 +12332,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="157" spans="1:20">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>1103</v>
       </c>
@@ -12362,7 +12394,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="158" spans="1:20">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A158" s="11">
         <v>1356</v>
       </c>
@@ -12424,7 +12456,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="159" spans="1:20">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>1222</v>
       </c>
@@ -12486,7 +12518,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="160" spans="1:20">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A160" s="11">
         <v>1043</v>
       </c>
@@ -12548,7 +12580,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="161" spans="1:20">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>1003</v>
       </c>
@@ -12610,7 +12642,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="162" spans="1:20">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A162" s="11">
         <v>1403</v>
       </c>
@@ -12672,7 +12704,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="163" spans="1:20">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>1101</v>
       </c>
@@ -12734,7 +12766,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="164" spans="1:20">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A164" s="11">
         <v>1001</v>
       </c>
@@ -12796,7 +12828,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>1190</v>
       </c>
@@ -12858,7 +12890,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A166" s="11">
         <v>1136</v>
       </c>
@@ -12920,7 +12952,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>1361</v>
       </c>
@@ -12982,7 +13014,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A168" s="11">
         <v>1349</v>
       </c>
@@ -13044,7 +13076,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>1293</v>
       </c>
@@ -13106,7 +13138,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="170" spans="1:20">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A170" s="11">
         <v>1406</v>
       </c>
@@ -13168,7 +13200,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>1192</v>
       </c>
@@ -13230,7 +13262,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="172" spans="1:20">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A172" s="11">
         <v>1422</v>
       </c>
@@ -13292,7 +13324,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="173" spans="1:20">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>1308</v>
       </c>
@@ -13354,7 +13386,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A174" s="11">
         <v>1342</v>
       </c>
@@ -13416,7 +13448,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="175" spans="1:20">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>1420</v>
       </c>
@@ -13478,7 +13510,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="176" spans="1:20">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A176" s="11">
         <v>1265</v>
       </c>
@@ -13540,7 +13572,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="177" spans="1:20">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>1159</v>
       </c>
@@ -13602,7 +13634,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="178" spans="1:20">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A178" s="11">
         <v>1115</v>
       </c>
@@ -13664,7 +13696,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="179" spans="1:20">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>1171</v>
       </c>
@@ -13726,7 +13758,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="180" spans="1:20">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A180" s="11">
         <v>1116</v>
       </c>
@@ -13788,7 +13820,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="181" spans="1:20">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>1150</v>
       </c>
@@ -13850,7 +13882,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="182" spans="1:20">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A182" s="11">
         <v>1080</v>
       </c>
@@ -13912,7 +13944,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="183" spans="1:20">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>1217</v>
       </c>
@@ -13974,7 +14006,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="184" spans="1:20">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A184" s="11">
         <v>1180</v>
       </c>
@@ -14036,7 +14068,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:20">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>1276</v>
       </c>
@@ -14098,7 +14130,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="186" spans="1:20">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A186" s="11">
         <v>1259</v>
       </c>
@@ -14160,7 +14192,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="187" spans="1:20">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>1268</v>
       </c>
@@ -14222,7 +14254,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="188" spans="1:20">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A188" s="11">
         <v>1100</v>
       </c>
@@ -14284,7 +14316,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="189" spans="1:20">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>1046</v>
       </c>
@@ -14346,7 +14378,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A190" s="11">
         <v>1278</v>
       </c>
@@ -14408,7 +14440,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>1200</v>
       </c>
@@ -14470,7 +14502,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A192" s="11">
         <v>1199</v>
       </c>
@@ -14532,7 +14564,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>1029</v>
       </c>
@@ -14594,7 +14626,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A194" s="11">
         <v>1004</v>
       </c>
@@ -14656,7 +14688,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>1128</v>
       </c>
@@ -14718,7 +14750,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A196" s="11">
         <v>1224</v>
       </c>
@@ -14780,7 +14812,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A197" s="12">
         <v>1149</v>
       </c>
@@ -14842,7 +14874,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A198" s="11">
         <v>1380</v>
       </c>
@@ -14904,7 +14936,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A199" s="12">
         <v>1090</v>
       </c>
@@ -14966,7 +14998,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A200" s="11">
         <v>1064</v>
       </c>
@@ -15028,7 +15060,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A201" s="12">
         <v>1211</v>
       </c>
@@ -15090,7 +15122,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A202" s="11">
         <v>1377</v>
       </c>
@@ -15152,7 +15184,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A203" s="12">
         <v>1169</v>
       </c>
@@ -15214,7 +15246,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A204" s="11">
         <v>1353</v>
       </c>
@@ -15276,7 +15308,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A205" s="12">
         <v>1294</v>
       </c>
@@ -15338,7 +15370,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A206" s="11">
         <v>1105</v>
       </c>
@@ -15400,7 +15432,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A207" s="12">
         <v>1340</v>
       </c>
@@ -15462,7 +15494,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A208" s="11">
         <v>1282</v>
       </c>
@@ -15524,7 +15556,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="209" spans="1:20">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A209" s="12">
         <v>1357</v>
       </c>
@@ -15586,7 +15618,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="210" spans="1:20">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A210" s="11">
         <v>1242</v>
       </c>
@@ -15644,7 +15676,7 @@
       </c>
       <c r="T210" s="11"/>
     </row>
-    <row r="211" spans="1:20">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A211" s="12">
         <v>1011</v>
       </c>
@@ -15706,7 +15738,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="212" spans="1:20">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A212" s="11">
         <v>1019</v>
       </c>
@@ -15768,7 +15800,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="213" spans="1:20">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A213" s="12">
         <v>1141</v>
       </c>
@@ -15826,7 +15858,7 @@
       </c>
       <c r="T213" s="12"/>
     </row>
-    <row r="214" spans="1:20">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A214" s="11">
         <v>1012</v>
       </c>
@@ -15888,7 +15920,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:20">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A215" s="12">
         <v>1272</v>
       </c>
@@ -15950,7 +15982,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="216" spans="1:20">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A216" s="11">
         <v>1338</v>
       </c>
@@ -16012,7 +16044,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="217" spans="1:20">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A217" s="12">
         <v>1309</v>
       </c>
@@ -16074,7 +16106,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="218" spans="1:20">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A218" s="11">
         <v>1352</v>
       </c>
@@ -16136,7 +16168,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="219" spans="1:20">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A219" s="12">
         <v>1337</v>
       </c>
@@ -16198,7 +16230,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="220" spans="1:20">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A220" s="11">
         <v>1215</v>
       </c>
@@ -16260,7 +16292,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="221" spans="1:20">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A221" s="12">
         <v>1267</v>
       </c>
@@ -16322,7 +16354,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="222" spans="1:20">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A222" s="11">
         <v>1236</v>
       </c>
@@ -16384,7 +16416,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="223" spans="1:20">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A223" s="12">
         <v>1032</v>
       </c>
@@ -16446,7 +16478,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="224" spans="1:20">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A224" s="11">
         <v>1038</v>
       </c>
@@ -16508,7 +16540,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="225" spans="1:20">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A225" s="12">
         <v>1358</v>
       </c>
@@ -16570,7 +16602,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="226" spans="1:20">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A226" s="11">
         <v>1401</v>
       </c>
@@ -16632,7 +16664,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="227" spans="1:20">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A227" s="12">
         <v>1205</v>
       </c>
@@ -16694,7 +16726,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="228" spans="1:20">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A228" s="11">
         <v>1346</v>
       </c>
@@ -16756,7 +16788,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="229" spans="1:20">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A229" s="12">
         <v>1247</v>
       </c>
@@ -16818,7 +16850,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="230" spans="1:20">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A230" s="11">
         <v>1119</v>
       </c>
@@ -16880,7 +16912,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="231" spans="1:20">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A231" s="12">
         <v>1074</v>
       </c>
@@ -16942,7 +16974,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="232" spans="1:20">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A232" s="11">
         <v>1400</v>
       </c>
@@ -17004,7 +17036,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="233" spans="1:20">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A233" s="12">
         <v>1301</v>
       </c>
@@ -17066,7 +17098,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="234" spans="1:20">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A234" s="11">
         <v>1237</v>
       </c>
@@ -17128,7 +17160,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="235" spans="1:20">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A235" s="12">
         <v>1246</v>
       </c>
@@ -17190,7 +17222,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="236" spans="1:20">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A236" s="11">
         <v>1374</v>
       </c>
@@ -17252,7 +17284,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="237" spans="1:20">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A237" s="12">
         <v>1318</v>
       </c>
@@ -17314,7 +17346,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="238" spans="1:20">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A238" s="11">
         <v>1319</v>
       </c>
@@ -17376,7 +17408,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="239" spans="1:20">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A239" s="12">
         <v>1344</v>
       </c>
@@ -17438,7 +17470,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="240" spans="1:20">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A240" s="11">
         <v>1175</v>
       </c>
@@ -17500,7 +17532,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:20">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A241" s="12">
         <v>1289</v>
       </c>
@@ -17562,7 +17594,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="242" spans="1:20">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A242" s="11">
         <v>1339</v>
       </c>
@@ -17624,7 +17656,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="243" spans="1:20">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A243" s="12">
         <v>1393</v>
       </c>
@@ -17686,7 +17718,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:20">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A244" s="11">
         <v>1118</v>
       </c>
@@ -17748,7 +17780,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="245" spans="1:20">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A245" s="12">
         <v>1087</v>
       </c>
@@ -17810,7 +17842,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="246" spans="1:20">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A246" s="11">
         <v>1428</v>
       </c>
@@ -17872,7 +17904,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="247" spans="1:20">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A247" s="12">
         <v>1277</v>
       </c>
@@ -17934,7 +17966,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="248" spans="1:20">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A248" s="11">
         <v>1254</v>
       </c>
@@ -17996,7 +18028,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="249" spans="1:20">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A249" s="12">
         <v>1109</v>
       </c>
@@ -18058,7 +18090,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="250" spans="1:20">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A250" s="11">
         <v>1367</v>
       </c>
@@ -18120,7 +18152,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="251" spans="1:20">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A251" s="12">
         <v>1111</v>
       </c>
@@ -18182,7 +18214,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="252" spans="1:20">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A252" s="11">
         <v>1364</v>
       </c>
@@ -18244,7 +18276,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="253" spans="1:20">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A253" s="12">
         <v>1157</v>
       </c>
@@ -18302,7 +18334,7 @@
       </c>
       <c r="T253" s="12"/>
     </row>
-    <row r="254" spans="1:20">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A254" s="11">
         <v>1094</v>
       </c>
@@ -18364,7 +18396,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="255" spans="1:20">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A255" s="12">
         <v>1207</v>
       </c>
@@ -18426,7 +18458,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="256" spans="1:20">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A256" s="11">
         <v>1322</v>
       </c>
@@ -18488,7 +18520,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="257" spans="1:20">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A257" s="12">
         <v>1193</v>
       </c>
@@ -18550,7 +18582,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="258" spans="1:20">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A258" s="11">
         <v>1412</v>
       </c>
@@ -18612,7 +18644,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="259" spans="1:20">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A259" s="12">
         <v>1216</v>
       </c>
@@ -18674,7 +18706,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="260" spans="1:20">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A260" s="11">
         <v>1300</v>
       </c>
@@ -18736,7 +18768,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="261" spans="1:20">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A261" s="12">
         <v>1243</v>
       </c>
@@ -18798,7 +18830,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="262" spans="1:20">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A262" s="11">
         <v>1274</v>
       </c>
@@ -18860,7 +18892,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="263" spans="1:20">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A263" s="12">
         <v>1228</v>
       </c>
@@ -18922,7 +18954,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="264" spans="1:20">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A264" s="11">
         <v>1250</v>
       </c>
@@ -18984,7 +19016,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="265" spans="1:20">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A265" s="12">
         <v>1102</v>
       </c>
@@ -19046,7 +19078,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="266" spans="1:20">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A266" s="11">
         <v>1188</v>
       </c>
@@ -19108,7 +19140,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="267" spans="1:20">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A267" s="12">
         <v>1049</v>
       </c>
@@ -19170,7 +19202,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="268" spans="1:20">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A268" s="11">
         <v>1183</v>
       </c>
@@ -19232,7 +19264,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="269" spans="1:20">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A269" s="12">
         <v>1391</v>
       </c>
@@ -19294,7 +19326,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="270" spans="1:20">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A270" s="11">
         <v>1158</v>
       </c>
@@ -19356,7 +19388,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="271" spans="1:20">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A271" s="12">
         <v>1386</v>
       </c>
@@ -19418,7 +19450,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:20">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A272" s="11">
         <v>1366</v>
       </c>
@@ -19480,7 +19512,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="273" spans="1:20">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A273" s="12">
         <v>1152</v>
       </c>
@@ -19542,7 +19574,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="274" spans="1:20">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A274" s="11">
         <v>1061</v>
       </c>
@@ -19604,7 +19636,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="275" spans="1:20">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A275" s="12">
         <v>1415</v>
       </c>
@@ -19666,7 +19698,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="276" spans="1:20">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A276" s="11">
         <v>1373</v>
       </c>
@@ -19728,7 +19760,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="277" spans="1:20">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A277" s="12">
         <v>1206</v>
       </c>
@@ -19790,7 +19822,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="278" spans="1:20">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A278" s="11">
         <v>1198</v>
       </c>
@@ -19852,7 +19884,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="279" spans="1:20">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A279" s="12">
         <v>1351</v>
       </c>
@@ -19914,7 +19946,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="280" spans="1:20">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A280" s="11">
         <v>1106</v>
       </c>
@@ -19976,7 +20008,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="281" spans="1:20">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A281" s="12">
         <v>1010</v>
       </c>
@@ -20038,7 +20070,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="282" spans="1:20">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A282" s="11">
         <v>1390</v>
       </c>
@@ -20100,7 +20132,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="283" spans="1:20">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A283" s="12">
         <v>1283</v>
       </c>
@@ -20162,7 +20194,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="284" spans="1:20">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A284" s="11">
         <v>1122</v>
       </c>
@@ -20224,7 +20256,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="285" spans="1:20">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A285" s="12">
         <v>1398</v>
       </c>
@@ -20286,7 +20318,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="286" spans="1:20">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A286" s="11">
         <v>1130</v>
       </c>
@@ -20348,7 +20380,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="287" spans="1:20">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A287" s="12">
         <v>1204</v>
       </c>
@@ -20410,7 +20442,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="288" spans="1:20">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A288" s="11">
         <v>1335</v>
       </c>
@@ -20472,7 +20504,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="289" spans="1:20">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A289" s="12">
         <v>1407</v>
       </c>
@@ -20534,7 +20566,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="290" spans="1:20">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A290" s="11">
         <v>1280</v>
       </c>
@@ -20596,7 +20628,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="291" spans="1:20">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A291" s="12">
         <v>1036</v>
       </c>
@@ -20658,7 +20690,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:20">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A292" s="11">
         <v>1028</v>
       </c>
@@ -20720,7 +20752,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="293" spans="1:20">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A293" s="12">
         <v>1307</v>
       </c>
@@ -20782,7 +20814,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="294" spans="1:20">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A294" s="11">
         <v>1375</v>
       </c>
@@ -20844,7 +20876,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="295" spans="1:20">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A295" s="12">
         <v>1024</v>
       </c>
@@ -20906,7 +20938,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="296" spans="1:20">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A296" s="11">
         <v>1326</v>
       </c>
@@ -20968,7 +21000,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="297" spans="1:20">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A297" s="12">
         <v>1066</v>
       </c>
@@ -21030,7 +21062,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="298" spans="1:20">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A298" s="11">
         <v>1291</v>
       </c>
@@ -21092,7 +21124,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="299" spans="1:20">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A299" s="12">
         <v>1166</v>
       </c>
@@ -21154,7 +21186,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="300" spans="1:20">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A300" s="11">
         <v>1231</v>
       </c>
@@ -21216,7 +21248,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="301" spans="1:20">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A301" s="12">
         <v>1381</v>
       </c>
@@ -21278,7 +21310,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="302" spans="1:20">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A302" s="11">
         <v>1315</v>
       </c>
@@ -21340,7 +21372,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="303" spans="1:20">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A303" s="12">
         <v>1324</v>
       </c>
@@ -21402,7 +21434,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="304" spans="1:20">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A304" s="11">
         <v>1137</v>
       </c>
@@ -21464,7 +21496,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="305" spans="1:20">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A305" s="12">
         <v>1232</v>
       </c>
@@ -21526,7 +21558,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="306" spans="1:20">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A306" s="11">
         <v>1245</v>
       </c>
@@ -21588,7 +21620,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="307" spans="1:20">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A307" s="12">
         <v>1235</v>
       </c>
@@ -21650,7 +21682,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="308" spans="1:20">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A308" s="11">
         <v>1041</v>
       </c>
@@ -21712,7 +21744,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="309" spans="1:20">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A309" s="12">
         <v>1014</v>
       </c>
@@ -21770,7 +21802,7 @@
       </c>
       <c r="T309" s="12"/>
     </row>
-    <row r="310" spans="1:20">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A310" s="11">
         <v>1078</v>
       </c>
@@ -21832,7 +21864,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="311" spans="1:20">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A311" s="12">
         <v>1165</v>
       </c>
@@ -21894,7 +21926,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="312" spans="1:20">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A312" s="11">
         <v>1054</v>
       </c>
@@ -21956,7 +21988,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:20">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A313" s="12">
         <v>1302</v>
       </c>
@@ -22018,7 +22050,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="314" spans="1:20">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A314" s="11">
         <v>1191</v>
       </c>
@@ -22080,7 +22112,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="315" spans="1:20">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A315" s="12">
         <v>1201</v>
       </c>
@@ -22142,7 +22174,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="316" spans="1:20">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A316" s="11">
         <v>1062</v>
       </c>
@@ -22204,7 +22236,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="317" spans="1:20">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A317" s="12">
         <v>1333</v>
       </c>
@@ -22266,7 +22298,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="318" spans="1:20">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A318" s="11">
         <v>1013</v>
       </c>
@@ -22328,7 +22360,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="319" spans="1:20">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A319" s="12">
         <v>1168</v>
       </c>
@@ -22390,7 +22422,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="320" spans="1:20">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A320" s="11">
         <v>1426</v>
       </c>
@@ -22452,7 +22484,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="321" spans="1:20">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A321" s="12">
         <v>1379</v>
       </c>
@@ -22514,7 +22546,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="322" spans="1:20">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A322" s="11">
         <v>1126</v>
       </c>
@@ -22572,7 +22604,7 @@
       </c>
       <c r="T322" s="11"/>
     </row>
-    <row r="323" spans="1:20">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A323" s="12">
         <v>1039</v>
       </c>
@@ -22634,7 +22666,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="324" spans="1:20">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A324" s="11">
         <v>1213</v>
       </c>
@@ -22696,7 +22728,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="325" spans="1:20">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A325" s="12">
         <v>1332</v>
       </c>
@@ -22758,7 +22790,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="326" spans="1:20">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A326" s="11">
         <v>1292</v>
       </c>
@@ -22820,7 +22852,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="327" spans="1:20">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A327" s="12">
         <v>1269</v>
       </c>
@@ -22882,7 +22914,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="328" spans="1:20">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A328" s="11">
         <v>1411</v>
       </c>
@@ -22944,7 +22976,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="329" spans="1:20">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A329" s="12">
         <v>1298</v>
       </c>
@@ -23006,7 +23038,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="330" spans="1:20">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A330" s="11">
         <v>1108</v>
       </c>
@@ -23068,7 +23100,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="331" spans="1:20">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A331" s="12">
         <v>1299</v>
       </c>
@@ -23130,7 +23162,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="332" spans="1:20">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A332" s="11">
         <v>1288</v>
       </c>
@@ -23192,7 +23224,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="333" spans="1:20">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A333" s="12">
         <v>1139</v>
       </c>
@@ -23254,7 +23286,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="334" spans="1:20">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A334" s="11">
         <v>1260</v>
       </c>
@@ -23316,7 +23348,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="335" spans="1:20">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A335" s="12">
         <v>1396</v>
       </c>
@@ -23378,7 +23410,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="336" spans="1:20">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A336" s="11">
         <v>1092</v>
       </c>
@@ -23440,7 +23472,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="337" spans="1:20">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A337" s="12">
         <v>1145</v>
       </c>
@@ -23502,7 +23534,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="338" spans="1:20">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A338" s="11">
         <v>1104</v>
       </c>
@@ -23564,7 +23596,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="339" spans="1:20">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A339" s="12">
         <v>1047</v>
       </c>
@@ -23626,7 +23658,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="340" spans="1:20">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A340" s="11">
         <v>1178</v>
       </c>
@@ -23688,7 +23720,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="341" spans="1:20">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A341" s="12">
         <v>1063</v>
       </c>
@@ -23750,7 +23782,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="342" spans="1:20">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A342" s="11">
         <v>1075</v>
       </c>
@@ -23808,7 +23840,7 @@
       </c>
       <c r="T342" s="11"/>
     </row>
-    <row r="343" spans="1:20">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A343" s="12">
         <v>1057</v>
       </c>
@@ -23870,7 +23902,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="344" spans="1:20">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A344" s="11">
         <v>1394</v>
       </c>
@@ -23932,7 +23964,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="345" spans="1:20">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A345" s="12">
         <v>1234</v>
       </c>
@@ -23994,7 +24026,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="346" spans="1:20">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A346" s="11">
         <v>1248</v>
       </c>
@@ -24056,7 +24088,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="347" spans="1:20">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A347" s="12">
         <v>1287</v>
       </c>
@@ -24118,7 +24150,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="348" spans="1:20">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A348" s="11">
         <v>1182</v>
       </c>
@@ -24180,7 +24212,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="349" spans="1:20">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A349" s="12">
         <v>1226</v>
       </c>
@@ -24242,7 +24274,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="350" spans="1:20">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A350" s="11">
         <v>1020</v>
       </c>
@@ -24304,7 +24336,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="351" spans="1:20">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A351" s="12">
         <v>1253</v>
       </c>
@@ -24366,7 +24398,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="352" spans="1:20">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A352" s="11">
         <v>1413</v>
       </c>
@@ -24428,7 +24460,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="353" spans="1:20">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A353" s="12">
         <v>1369</v>
       </c>
@@ -24490,7 +24522,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="354" spans="1:20">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A354" s="11">
         <v>1392</v>
       </c>
@@ -24552,7 +24584,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="355" spans="1:20">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A355" s="12">
         <v>1083</v>
       </c>
@@ -24614,7 +24646,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="356" spans="1:20">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A356" s="11">
         <v>1384</v>
       </c>
@@ -24676,7 +24708,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="357" spans="1:20">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A357" s="12">
         <v>1240</v>
       </c>
@@ -24738,7 +24770,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="358" spans="1:20">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A358" s="11">
         <v>1018</v>
       </c>
@@ -24800,7 +24832,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="359" spans="1:20">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A359" s="12">
         <v>1093</v>
       </c>
@@ -24858,7 +24890,7 @@
       </c>
       <c r="T359" s="12"/>
     </row>
-    <row r="360" spans="1:20">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A360" s="11">
         <v>1117</v>
       </c>
@@ -24920,7 +24952,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="361" spans="1:20">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A361" s="12">
         <v>1360</v>
       </c>
@@ -24982,7 +25014,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="362" spans="1:20">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A362" s="11">
         <v>1076</v>
       </c>
@@ -25044,7 +25076,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="363" spans="1:20">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A363" s="12">
         <v>1096</v>
       </c>
@@ -25106,7 +25138,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="364" spans="1:20">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A364" s="11">
         <v>1027</v>
       </c>
@@ -25168,7 +25200,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="365" spans="1:20">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A365" s="12">
         <v>1225</v>
       </c>
@@ -25230,7 +25262,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="366" spans="1:20">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A366" s="11">
         <v>1325</v>
       </c>
@@ -25292,7 +25324,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="367" spans="1:20">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A367" s="12">
         <v>1336</v>
       </c>
@@ -25354,7 +25386,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="368" spans="1:20">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A368" s="11">
         <v>1284</v>
       </c>
@@ -25416,7 +25448,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="369" spans="1:20">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A369" s="12">
         <v>1077</v>
       </c>
@@ -25478,7 +25510,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="370" spans="1:20">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A370" s="11">
         <v>1251</v>
       </c>
@@ -25540,7 +25572,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="371" spans="1:20">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A371" s="12">
         <v>1161</v>
       </c>
@@ -25602,7 +25634,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="372" spans="1:20">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A372" s="11">
         <v>1084</v>
       </c>
@@ -25664,7 +25696,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="373" spans="1:20">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A373" s="12">
         <v>1223</v>
       </c>
@@ -25726,7 +25758,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="374" spans="1:20">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A374" s="11">
         <v>1382</v>
       </c>
@@ -25788,7 +25820,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="375" spans="1:20">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A375" s="12">
         <v>1264</v>
       </c>
@@ -25850,7 +25882,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:20">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A376" s="11">
         <v>1135</v>
       </c>
@@ -25912,7 +25944,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="377" spans="1:20">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A377" s="12">
         <v>1313</v>
       </c>
@@ -25974,7 +26006,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="378" spans="1:20">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A378" s="11">
         <v>1134</v>
       </c>
@@ -26036,7 +26068,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="379" spans="1:20">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A379" s="12">
         <v>1144</v>
       </c>
@@ -26098,7 +26130,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="380" spans="1:20">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A380" s="11">
         <v>1220</v>
       </c>
@@ -26160,7 +26192,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="381" spans="1:20">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A381" s="12">
         <v>1184</v>
       </c>
@@ -26222,7 +26254,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="382" spans="1:20">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A382" s="11">
         <v>1143</v>
       </c>
@@ -26284,7 +26316,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="383" spans="1:20">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A383" s="12">
         <v>1255</v>
       </c>
@@ -26346,7 +26378,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="384" spans="1:20">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A384" s="11">
         <v>1065</v>
       </c>
@@ -26408,7 +26440,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="385" spans="1:20">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A385" s="12">
         <v>1022</v>
       </c>
@@ -26470,7 +26502,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="386" spans="1:20">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A386" s="11">
         <v>1160</v>
       </c>
@@ -26532,7 +26564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="387" spans="1:20">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A387" s="12">
         <v>1059</v>
       </c>
@@ -26594,7 +26626,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="388" spans="1:20">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A388" s="11">
         <v>1397</v>
       </c>
@@ -26656,7 +26688,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="389" spans="1:20">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A389" s="12">
         <v>1072</v>
       </c>
@@ -26718,7 +26750,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="390" spans="1:20">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A390" s="11">
         <v>1221</v>
       </c>
@@ -26776,7 +26808,7 @@
       </c>
       <c r="T390" s="11"/>
     </row>
-    <row r="391" spans="1:20">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A391" s="12">
         <v>1271</v>
       </c>
@@ -26838,7 +26870,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="392" spans="1:20">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A392" s="11">
         <v>1414</v>
       </c>
@@ -26900,7 +26932,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="393" spans="1:20">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A393" s="12">
         <v>1162</v>
       </c>
@@ -26962,7 +26994,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="394" spans="1:20">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A394" s="11">
         <v>1045</v>
       </c>
@@ -27024,7 +27056,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="395" spans="1:20">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A395" s="12">
         <v>1402</v>
       </c>
@@ -27086,7 +27118,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="396" spans="1:20">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A396" s="11">
         <v>1239</v>
       </c>
@@ -27148,7 +27180,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="397" spans="1:20">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A397" s="12">
         <v>1173</v>
       </c>
@@ -27210,7 +27242,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="398" spans="1:20">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A398" s="11">
         <v>1252</v>
       </c>
@@ -27272,7 +27304,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="399" spans="1:20">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A399" s="12">
         <v>1257</v>
       </c>
@@ -27334,7 +27366,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="400" spans="1:20">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A400" s="11">
         <v>1086</v>
       </c>
@@ -27396,7 +27428,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="401" spans="1:20">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A401" s="12">
         <v>1133</v>
       </c>
@@ -27458,7 +27490,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="402" spans="1:20">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A402" s="11">
         <v>1091</v>
       </c>
@@ -27520,7 +27552,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="403" spans="1:20">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A403" s="12">
         <v>1297</v>
       </c>
@@ -27582,7 +27614,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="404" spans="1:20">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A404" s="11">
         <v>1021</v>
       </c>
@@ -27644,7 +27676,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="405" spans="1:20">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A405" s="12">
         <v>1286</v>
       </c>
@@ -27706,7 +27738,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="406" spans="1:20">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A406" s="11">
         <v>1067</v>
       </c>
@@ -27768,7 +27800,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="407" spans="1:20">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A407" s="12">
         <v>1189</v>
       </c>
@@ -27830,7 +27862,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="408" spans="1:20">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A408" s="11">
         <v>1417</v>
       </c>
@@ -27892,7 +27924,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="409" spans="1:20">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A409" s="12">
         <v>1202</v>
       </c>
@@ -27954,7 +27986,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="410" spans="1:20">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A410" s="11">
         <v>1154</v>
       </c>
@@ -28016,7 +28048,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="411" spans="1:20">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A411" s="12">
         <v>1195</v>
       </c>
@@ -28078,7 +28110,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="412" spans="1:20">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A412" s="11">
         <v>1317</v>
       </c>
@@ -28140,7 +28172,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="413" spans="1:20">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A413" s="12">
         <v>1258</v>
       </c>
@@ -28202,7 +28234,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="414" spans="1:20">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A414" s="11">
         <v>1129</v>
       </c>
@@ -28264,7 +28296,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="415" spans="1:20">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A415" s="12">
         <v>1002</v>
       </c>
@@ -28326,7 +28358,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="416" spans="1:20">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A416" s="11">
         <v>1023</v>
       </c>
@@ -28388,7 +28420,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="417" spans="1:20">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A417" s="12">
         <v>1383</v>
       </c>
@@ -28450,7 +28482,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="418" spans="1:20">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A418" s="11">
         <v>1363</v>
       </c>
@@ -28512,7 +28544,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="419" spans="1:20">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A419" s="12">
         <v>1306</v>
       </c>
@@ -28574,7 +28606,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="420" spans="1:20">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A420" s="11">
         <v>1410</v>
       </c>
@@ -28636,7 +28668,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="421" spans="1:20">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A421" s="12">
         <v>1343</v>
       </c>
@@ -28698,7 +28730,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="422" spans="1:20">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A422" s="11">
         <v>1310</v>
       </c>
@@ -28760,7 +28792,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="423" spans="1:20">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A423" s="12">
         <v>1181</v>
       </c>
@@ -28822,7 +28854,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="424" spans="1:20">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A424" s="11">
         <v>1241</v>
       </c>
@@ -28884,7 +28916,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="425" spans="1:20">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A425" s="12">
         <v>1120</v>
       </c>
@@ -28946,7 +28978,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="426" spans="1:20">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A426" s="11">
         <v>1170</v>
       </c>
@@ -29008,7 +29040,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="427" spans="1:20">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A427" s="12">
         <v>1026</v>
       </c>
@@ -29070,7 +29102,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="428" spans="1:20">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A428" s="11">
         <v>1030</v>
       </c>
@@ -29132,7 +29164,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="429" spans="1:20">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A429" s="12">
         <v>1285</v>
       </c>
@@ -29194,7 +29226,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="430" spans="1:20">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A430" s="11">
         <v>1048</v>
       </c>
@@ -29256,7 +29288,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="431" spans="1:20">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A431" s="12">
         <v>1037</v>
       </c>
@@ -29318,7 +29350,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="432" spans="1:20">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A432" s="11">
         <v>1131</v>
       </c>
@@ -29380,7 +29412,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="433" spans="1:20">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A433" s="12">
         <v>1305</v>
       </c>
@@ -29442,7 +29474,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="434" spans="1:20">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A434" s="11">
         <v>1376</v>
       </c>
@@ -29515,7 +29547,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -29526,31 +29558,31 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="49" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+    </row>
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
         <v>520</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.95" customHeight="1">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>521</v>
       </c>
@@ -29576,7 +29608,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="51.95" customHeight="1">
+    <row r="4" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>529</v>
       </c>
@@ -29590,7 +29622,7 @@
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:8" ht="51.95" customHeight="1">
+    <row r="5" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>531</v>
       </c>
@@ -29604,7 +29636,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:8" ht="51.95" customHeight="1">
+    <row r="6" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>533</v>
       </c>
@@ -29618,12 +29650,12 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="51.95" customHeight="1">
+    <row r="7" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>535</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>536</v>
+        <v>576</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -29632,9 +29664,9 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:8" ht="36" customHeight="1">
+    <row r="8" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -29644,9 +29676,9 @@
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
     </row>
-    <row r="9" spans="1:8" ht="36" customHeight="1">
+    <row r="9" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -29656,9 +29688,9 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8" ht="36" customHeight="1">
+    <row r="10" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -29668,9 +29700,9 @@
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:8" ht="36" customHeight="1">
+    <row r="11" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -29680,9 +29712,9 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="36" customHeight="1">
+    <row r="12" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -29692,18 +29724,18 @@
       <c r="G12" s="20"/>
       <c r="H12" s="20"/>
     </row>
-    <row r="13" spans="1:8" ht="14.1" customHeight="1"/>
-    <row r="14" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A14" s="47" t="s">
-        <v>542</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
+    <row r="13" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -29718,7 +29750,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -29740,55 +29772,55 @@
     <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="32.1" customHeight="1">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="52" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+    </row>
+    <row r="2" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="50" t="s">
         <v>543</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-    </row>
-    <row r="2" spans="1:20" ht="24" customHeight="1">
-      <c r="A2" s="47" t="s">
-        <v>544</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>33</v>
       </c>
@@ -29850,7 +29882,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -29872,7 +29904,7 @@
       <c r="S4" s="23"/>
       <c r="T4" s="23"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -29894,7 +29926,7 @@
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
@@ -29916,7 +29948,7 @@
       <c r="S6" s="23"/>
       <c r="T6" s="23"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="24"/>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
@@ -29938,7 +29970,7 @@
       <c r="S7" s="24"/>
       <c r="T7" s="24"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -29960,7 +29992,7 @@
       <c r="S8" s="23"/>
       <c r="T8" s="23"/>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
@@ -29982,7 +30014,7 @@
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -30004,7 +30036,7 @@
       <c r="S10" s="23"/>
       <c r="T10" s="23"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="24"/>
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
@@ -30026,7 +30058,7 @@
       <c r="S11" s="24"/>
       <c r="T11" s="24"/>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -30048,7 +30080,7 @@
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="24"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -30070,7 +30102,7 @@
       <c r="S13" s="24"/>
       <c r="T13" s="24"/>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -30092,7 +30124,7 @@
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="24"/>
       <c r="B15" s="24"/>
       <c r="C15" s="24"/>
@@ -30114,7 +30146,7 @@
       <c r="S15" s="24"/>
       <c r="T15" s="24"/>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
@@ -30136,7 +30168,7 @@
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
@@ -30158,7 +30190,7 @@
       <c r="S17" s="24"/>
       <c r="T17" s="24"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -30180,7 +30212,7 @@
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -30202,7 +30234,7 @@
       <c r="S19" s="24"/>
       <c r="T19" s="24"/>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -30224,7 +30256,7 @@
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="24"/>
       <c r="B21" s="24"/>
       <c r="C21" s="24"/>
@@ -30246,7 +30278,7 @@
       <c r="S21" s="24"/>
       <c r="T21" s="24"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
@@ -30268,7 +30300,7 @@
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="24"/>
       <c r="B23" s="24"/>
       <c r="C23" s="24"/>
@@ -30290,7 +30322,7 @@
       <c r="S23" s="24"/>
       <c r="T23" s="24"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
@@ -30312,7 +30344,7 @@
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="24"/>
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
@@ -30334,7 +30366,7 @@
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -30356,7 +30388,7 @@
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="24"/>
       <c r="B27" s="24"/>
       <c r="C27" s="24"/>
@@ -30378,7 +30410,7 @@
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="23"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -30400,7 +30432,7 @@
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -30422,7 +30454,7 @@
       <c r="S29" s="24"/>
       <c r="T29" s="24"/>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
@@ -30444,7 +30476,7 @@
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="24"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
@@ -30466,7 +30498,7 @@
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
@@ -30488,7 +30520,7 @@
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="24"/>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
@@ -30522,7 +30554,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -30530,198 +30562,198 @@
     <col min="6" max="6" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="8.1" customHeight="1"/>
-    <row r="2" spans="2:5" ht="38.1" customHeight="1">
-      <c r="B2" s="42" t="s">
+    <row r="1" spans="2:5" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:5" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="43" t="s">
+        <v>544</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+    </row>
+    <row r="3" spans="2:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="54" t="s">
         <v>545</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-    </row>
-    <row r="3" spans="2:5" ht="21.95" customHeight="1">
-      <c r="B3" s="51" t="s">
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+    </row>
+    <row r="4" spans="2:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="25" t="s">
         <v>546</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-    </row>
-    <row r="4" spans="2:5" ht="12" customHeight="1"/>
-    <row r="5" spans="2:5" ht="21.95" customHeight="1">
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="D5" s="26" t="s">
         <v>548</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>549</v>
       </c>
-      <c r="E5" s="26" t="s">
+    </row>
+    <row r="6" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="27" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="36" customHeight="1">
-      <c r="B6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="D6" s="28" t="s">
         <v>552</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="E6" s="28" t="s">
         <v>553</v>
       </c>
-      <c r="E6" s="28" t="s">
+    </row>
+    <row r="7" spans="2:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="29" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="54" customHeight="1">
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="D7" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="E7" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="E7" s="30" t="s">
+    </row>
+    <row r="8" spans="2:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="31" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="39" customHeight="1">
-      <c r="B8" s="31" t="s">
+      <c r="C8" s="31" t="s">
         <v>559</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="D8" s="31" t="s">
         <v>560</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E8" s="31" t="s">
         <v>561</v>
       </c>
-      <c r="E8" s="31" t="s">
+    </row>
+    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="55" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" ht="14.1" customHeight="1"/>
-    <row r="10" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B10" s="52" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+    </row>
+    <row r="11" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="32" t="s">
         <v>563</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-    </row>
-    <row r="11" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B11" s="32" t="s">
+      <c r="C11" s="58"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="33" t="s">
+    </row>
+    <row r="12" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="34" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B12" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="34" t="s">
+    <row r="13" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="32" t="s">
+        <v>553</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="33" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B13" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="33" t="s">
+    <row r="14" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="58"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="34" t="s">
         <v>568</v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="34" t="s">
+    </row>
+    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="60" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" ht="14.1" customHeight="1"/>
-    <row r="16" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B16" s="57" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+    </row>
+    <row r="17" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="35" t="s">
         <v>570</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-    </row>
-    <row r="17" spans="2:5" ht="27.95" customHeight="1">
-      <c r="B17" s="35" t="s">
-        <v>571</v>
-      </c>
-      <c r="C17" s="53" t="str">
+      <c r="C17" s="56" t="str">
         <f>IF(AND(C12&lt;&gt;"",C13&lt;&gt;""),C12/(C13/10),"Enter stats above")</f>
         <v>Enter stats above</v>
       </c>
-      <c r="D17" s="60"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="36" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="27.95" customHeight="1">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="37" t="s">
-        <v>552</v>
-      </c>
-      <c r="C18" s="54" t="str">
+        <v>551</v>
+      </c>
+      <c r="C18" s="57" t="str">
         <f>IF(C12&lt;&gt;"",C12,"Enter stats above")</f>
         <v>Enter stats above</v>
       </c>
-      <c r="D18" s="60"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="34" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="27.95" customHeight="1">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
-        <v>553</v>
-      </c>
-      <c r="C19" s="56" t="str">
+        <v>552</v>
+      </c>
+      <c r="C19" s="59" t="str">
         <f>IF(C14&lt;&gt;"",C14/82,"Enter stats above")</f>
         <v>Enter stats above</v>
       </c>
-      <c r="D19" s="60"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="36" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="27.95" customHeight="1">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="37" t="s">
-        <v>554</v>
-      </c>
-      <c r="C20" s="54" t="str">
+        <v>553</v>
+      </c>
+      <c r="C20" s="57" t="str">
         <f>IF(C13&lt;&gt;"",C13,"Enter stats above")</f>
         <v>Enter stats above</v>
       </c>
-      <c r="D20" s="60"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="34" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="53" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" ht="14.1" customHeight="1"/>
-    <row r="22" spans="2:5" ht="36" customHeight="1">
-      <c r="B22" s="50" t="s">
-        <v>576</v>
-      </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -30744,15 +30776,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B333CA68795B2448D7896641ADDBF80" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5564d2453dc004a81f446ba6e8578091">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4d82564-f888-4a2a-ae0f-8086d18988c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="805196b184fd9662ed0ff4f249bd3f51" ns2:_="">
     <xsd:import namespace="c4d82564-f888-4a2a-ae0f-8086d18988c0"/>
@@ -30890,6 +30913,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -30897,13 +30929,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC4F442-581A-43DE-ACA5-18F778330AA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02FD89A-02F8-4757-85C0-1631533E5300}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c4d82564-f888-4a2a-ae0f-8086d18988c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02FD89A-02F8-4757-85C0-1631533E5300}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC4F442-581A-43DE-ACA5-18F778330AA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E5E020-0E27-4681-8015-C0762EEF03CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E5E020-0E27-4681-8015-C0762EEF03CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>